--- a/산업안전기사_작업형_문제은행.xlsx
+++ b/산업안전기사_작업형_문제은행.xlsx
@@ -8,46 +8,62 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE11DEE4-2747-4F93-8853-EBECF6AEB7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D3F4FC-FAFA-4696-9AE5-8068A590BACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="17년 과년도" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>점수</t>
+  </si>
+  <si>
+    <t>정답</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출제빈도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
   <si>
     <t>문제</t>
-  </si>
-  <si>
-    <t>해설</t>
-  </si>
-  <si>
-    <t>점수</t>
-  </si>
-  <si>
-    <t>해설이미지</t>
-  </si>
-  <si>
-    <t>문제이미지</t>
-  </si>
-  <si>
-    <t>보기</t>
-  </si>
-  <si>
-    <t>[보기]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림설명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그림 및 동영상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 이동식 크레인을 사용하여 철제 배관을 인양하는 작업으로 신호수의 신호에 따라 철제 배관을 인양 중 H빔에 부딪치면서 흔들리는 동영상이다. 배관 인양 작업시 위험요인 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 와이어로프의 안전상태가 불안정하여 위험하다.
+② 작업 반경 내 관계근로자 이외의 외부 작업자가 출입하여 위험하다.
+③ 훅의 해지장치 및 안전상태가 불안정하여 위험하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -56,14 +72,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -78,7 +101,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,29 +109,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -412,34 +430,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="35.5" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1">
+      <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="87">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5">
         <v>6</v>
       </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/산업안전기사_작업형_문제은행.xlsx
+++ b/산업안전기사_작업형_문제은행.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D3F4FC-FAFA-4696-9AE5-8068A590BACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DCC258-5C43-4A44-9515-20BE0F5D0D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="17년 과년도" sheetId="1" r:id="rId1"/>
+    <sheet name="18년 과년도" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>점수</t>
   </si>
@@ -30,10 +31,6 @@
   </si>
   <si>
     <t>참고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>출제빈도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -56,6 +53,155 @@
     <t>① 와이어로프의 안전상태가 불안정하여 위험하다.
 ② 작업 반경 내 관계근로자 이외의 외부 작업자가 출입하여 위험하다.
 ③ 훅의 해지장치 및 안전상태가 불안정하여 위험하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 지게차에 경유를 주입하는 동안에 운전자가 시동을 건 채 내려 다른 작업자와 흡연을 하며 이야기를 나누고 있음을 나타내고 있다. 이 화면에서 지게차 운전자의 흡연(담뱃불)에 해당하는 발화원의 형태를 무엇이라 하는지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면을 보고 지게차 주행안전작업 사항 중 잘못된 내용(사고위험요인)을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전방의 시야 불충분으로 지게차에 의해 작업자가 다칠 수 있다.
+② 물건을 과적하여 운전자의 시야를 가려 다른 작업자가 다칠 수 있다.
+③ 물건을 불안정하게 적재하여 화물이 떨어져 다른 작업자가 다칠 수 있다.
+④ 다른 작업자가 작업통로에 나와서 작업을 하고 있어 지게차에 의해 다칠 수 있다.
+⑤ 난폭한 운전, 과속으로 운전자 본인이 다치거나 다른 작업자가 다칠 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 크랭크 프레스로 철판에 구멍을 뚫는 작업을 하고 있다. 위험 예지 포인트(핵심위험요인)를 3가지 적으시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 프레스 페달을 발로 밟아 프레스의 슬라이드가 작동해 손을 다친다.
+② 금형에 붙어 있는 이물질을 제거하려다 손을 다친다.
+③ 금형에 붙어 있는 이물질을 제거하려다 눈에 이물질이 들어가 눈을 다친다.
+④ 주변정리가 되어 있지 않아 주변의 물건에 발이 걸려 넘어져 프레스 기계에 부딪친다.
+⑤ 작업자의 실수로 슬라이드가 하강하여 작업자가 다친다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에서 가압상태의 LPG가 대기 중에 유출되어 순간적으로 기화가 일어나 점화원에 의해 발생하는 ① 폭발의 종류 ② 폭발의 원인을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 폭발의 종류 : 증기운 폭발(UVCE : Unconfined Vapor Cloud Explosion)
+② 폭발의 원인 :
+ - 저온 액화가스의 저장태크나 고압의 인화성 액체용기가 파괴되어 다량의 인화성 증기가 폐쇄공간이 아닌 대기중으로 급격히 방출되어 공기 중에 분산 확산되어 있는 상태
+ - 인화성 가스 또는 기화하기 쉬운 인화성 액체 등이저장된 고압가스 용기(저장태크)의 파괴로 인하여 대기중으로 유출된 인화성 증기가 구름을 형성(증기운)한 상태에서 점화원이 증기운에 접촉하여 폭발(가스폭발)하는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 활선작업에 대한 동영상이다. 이와 같이 활선작업시 내재되어 있는 핵심 위험 요인을 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업자의 복장이 갖추어져 있지 않았다.
+② 신호전달이 잘 이루어지지 않았다.
+③ 작업자가 안전확인(활선 또는 사선)을 소홀히 했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 작업자 2명이 전주에서 활선작업을 하고 있다. 작업자 1명은 밑에서 절연방호구를 다른 작업자 1명은 크레인 위에서 물건을 받아 활선에 절연방호구 설치 작업을 하다 감전사고가 발생한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 30[kV] 전압이 흐르고 고압선 아래에서 작업 중 발생한 재해사례이다. 크레인을 이용하여 고압선 주위에서 작업할 경우 사업주의 감전 조치사항(동종 재해예방을 위한 작업지휘자) 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식크레인으로 작업하다 붐대가 전선에 닿아 감전되는 동영상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 창량 등을 충전부로붜 300[cm] 이상 이격시키되, 대지전압이 50[kV]를 넘는 경우 10[kV} 증가할 때마다 10[cm]씩 증가한다.
+② 접지된 차량등이 충전전로와 접촉할 우려가 있을 경우 지상의 근로자가 접지점에 접촉하지 않도록 조치한다.
+③ 차량과 근로자가 접촉하지 않도록 방책을 설치하거나 감시인을 배치한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 아파트 창틀에서 작업 중 발생한 재해사례이다. 이 영상의 작업자의 추락사고 원인 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상에서 작업자 A, B가 작업을 하고 있다. 창틀에서 작업 중인 A가 처마 위에 있는 B에게 작업발판을 건네준 후 B가 있는 옆 처마 위로 이동하다 발을 헛디뎌 바닥으로 추락하는 장면이다.(주변이 정리정돈 되어있지 않고, A작업자가 밟고 있던 콘크리트 부스러기가 추락할 때 같이 떨어진다.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전난간 미설치
+② 안전대 미착용
+③ 추락방호망 미설치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상에서 C보호구의 사용 장소에 따른 분류2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 도금작업에 사용하는 보호구 사진 A, B, C 3가지를 보여준 후, C 보호구(고무제안전화)에 노란색 동그라미가 표시되면서 정지된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[구분 / 사용장소]
+ㆍ일반용 / 일반작업장
+ㆍ내유용 / 탄화수소류의 윤활유 등을 취급하는 작업장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 덤프트럭 적재함을 올리고 실린더 유압장치 밸브를 수리하던 중 발생한 재해사례이다. 동영상과 같이 차량계 하역운반기계 등의 수리 또는 부속장치의 장착 및 해체작업을 하는 때에 작업지휘자의 준수사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운전석에서 내려 덤프트럭 적재함을 올리고 실린더 유압장치 밸브를 수리하던 중 적재함 사이에 끼임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 포크ㆍ버킷ㆍ암 또는 이들에 의하여 지지되어 있는 화물의 밑에 근로자를 출입시키지 말것
+② 작업순서를 결정하고 작업을 지휘할 것
+③ 안전지주 또는 안전블록 등의 사용상황 등을 점검할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식크레인작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지게차경유주입.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지게차주행.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>크랭크프레스작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LPG화재.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활선작업보후구및활선작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식크레인작업1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아파트창틀작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도금작업보호구.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -63,7 +209,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +238,12 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -113,20 +265,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,55 +581,230 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="35.5" customWidth="1"/>
-    <col min="2" max="2" width="13.69921875" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.296875" customWidth="1"/>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="87">
-      <c r="A2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5">
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1">
         <v>6</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+    </row>
+    <row r="6" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="113.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E1CD94-D288-4A57-AC69-EDD02BC9BCAA}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/산업안전기사_작업형_문제은행.xlsx
+++ b/산업안전기사_작업형_문제은행.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DCC258-5C43-4A44-9515-20BE0F5D0D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A424AC-F56B-4F8E-BA1A-488F710FBAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="17년 과년도" sheetId="1" r:id="rId1"/>
     <sheet name="18년 과년도" sheetId="2" r:id="rId2"/>
+    <sheet name="19년 과년도" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
   <si>
     <t>점수</t>
   </si>
@@ -204,12 +205,139 @@
     <t>도금작업보호구.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>화면은 DMF 작업장에서 한 작업자가 방독마스크, 안전장갑, 보호복 등을 착용하지 않은 채 유해물질 DMF 작업을 하고 있다. 피부자극성 및 부식성 관리대상 유해물질 취급시 비치하여야 할 보호장구 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 불침투성 보호장갑
+② 불침투성 보호복
+③ 불침투성 보호장화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업자가 전주에 올라가다 표지판에 부딪혀 추락하는 재해가 발생했였다. 재해발생 원인 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락방지대 미착용 및 수직구명줄 미설치로 재해발생
+② 안전대 또는 고소작업대를 사용하지 않아 재해발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 고소작업대 작업을 하고 있다. 고소작업대 작업시 작업시작전 점검사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 비상정지장치 및 비상하강 방지장치 기능의 이상 유무
+② 과부하 방지장치의 작동 유무(와이어로프 또는 체인구동방식의 경우
+③ 아우트리거 또는 바퀴의 이상 유무
+④ 작업면의 기울기 또는 요철 유무
+⑤ 활선작업용 장치의 경우 홈ㆍ균열ㆍ파손 등 그 밖의 손상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상에서 항타기 또는 항발기 조립시 점검사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 본체연결부의 풀림 또는 손상의 유무
+② 권상용 와이어로프 ㆍ드럼 및 도르래의 부착상태의 이상유무
+③ 권상장치의 브레이크 및 쐐기장치 기능의 이상유무
+④ 권상기의 설치상태의 이상유무
+⑤ 버팀의 방법 및 고정상태의 이상유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사진은 유해물질에 근로자가 노출되는 것을 막기 위하여 사용하는 방독마스크이다. 사진을 참고하여 보호구 성능검정 규정에 따른 각 물음에 답하시오.(단, 정화통의 외부측면은 녹색)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 방독마스크의 종류를 쓰시오.
+② 방독마스크 정화통의 주성분(흡수제)을 1가지만 쓰시오.
+③ 방독마스크 정화통의 시험가스를 1가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 암모니아용
+② 큐프라마이트
+③ 암모니아(NH₃)가스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 승강기 컨트롤 패널을 맨손으로 점검(전압측정) 중 발생한 재해사례이다. 감전 방지대책 3가지를 서술하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 각 차단기별로 회로명을 표기하여 오동작을 막는다.
+② 잠금장치(시건장치) 및 표찰(TAG)을 사용하여 해당자 이외에 오작동을 막는다.
+③ 작업자에게 해당 작업시의 전기위험에 대한 안저교육을 실시한다.
+④ 작업자 간의 정확성을 기하기 위해 무전기 등의 연락가능장비를 이용하여 여러 차례 확인하는 절차를 준수한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사진은 교각공사 등의 철근조립(가공)작업 방법을 보여주고 있다. 철근작업시 준수사항 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 철근가공 작업장 주위는 작업책임자가 상주하여야 하고 정정돈되어 있어야 하며, 작업원 이외는 출입을 금지하여야 한다.
+② 가공 작업자는 안전모 및 안전보호장구를 착용하여야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 자동차부품을 도금한 후 세척하는 과정이다. 이 영상을 참고하여 위험예지훈련을 하고자한다면 이와 연관된 행동목표 2가지만 제시하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업 중 흡연을 하지 말자.
+② 세척 작업시 불침투성 보호(의)복을 착용하자.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면 속 작업자는 교류아크용접 작업을 진행하고 있다. 이 용접기의 방호장치 자동전격방지기 종류 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 외장형
+② 내장형
+③ 저자항시동형(L형)
+④ 고저항시동형(H형)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사진 보호구를 참고하여 [보기] 안전모 시험성능기준 ①, ②, ③의 (   )를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 9.5
+② 11.1
+③ 4,450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전모 시험성능기준.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 영상표시단말기(VDT) 작업에 관한 영상이다. 동영상을 참고하여 개선해야 할 사항을 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업자가 의자의 등받이에 충분히 지지되어 있지 않다.
+② 모니터가 보기 편한 위치에 조정되어 있지 않다.
+③ 키보드가 조작하기 편한 위치에 놓여 있지 않다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,7 +710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
@@ -592,7 +720,7 @@
     <col min="6" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -612,7 +740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="87" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="87">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -626,7 +754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="104.4">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -640,7 +768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="174">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -654,7 +782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="139.19999999999999" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="139.19999999999999">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -668,7 +796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="174" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="174">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -682,7 +810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="113.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="113.4" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -699,7 +827,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="121.8">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -716,7 +844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="121.8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="121.8">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -733,7 +861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="52.2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="52.2">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -758,18 +886,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E1CD94-D288-4A57-AC69-EDD02BC9BCAA}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
     <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="1"/>
+    <col min="6" max="6" width="38.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -786,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="104.4" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -803,6 +932,174 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" ht="104.4">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2">
+      <c r="A4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="121.8">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="104.4">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="121.8">
+      <c r="A8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="69.599999999999994">
+      <c r="A9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="69.599999999999994">
+      <c r="A10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2433A3-894D-42EC-B9D8-5384B49B20B8}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="69.599999999999994">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="52.2">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="1">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2">
+      <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/산업안전기사_작업형_문제은행.xlsx
+++ b/산업안전기사_작업형_문제은행.xlsx
@@ -2,27 +2,32 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A424AC-F56B-4F8E-BA1A-488F710FBAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B4CE5F-286C-4B6D-9C61-3B9CE0716B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="17년 과년도" sheetId="1" r:id="rId1"/>
     <sheet name="18년 과년도" sheetId="2" r:id="rId2"/>
     <sheet name="19년 과년도" sheetId="3" r:id="rId3"/>
+    <sheet name="20년 과년도" sheetId="4" r:id="rId4"/>
+    <sheet name="21년 과년도" sheetId="5" r:id="rId5"/>
+    <sheet name="22년 과년도" sheetId="6" r:id="rId6"/>
+    <sheet name="23년 과년도" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="208">
   <si>
     <t>점수</t>
   </si>
@@ -330,6 +335,693 @@
     <t>① 작업자가 의자의 등받이에 충분히 지지되어 있지 않다.
 ② 모니터가 보기 편한 위치에 조정되어 있지 않다.
 ③ 키보드가 조작하기 편한 위치에 놓여 있지 않다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 건물해체에 관한 장면으로 작업자가 위험부분에 머무르는 것이 사고요인으로 판단된다. 동종사고 예방차원에서 작업자는 하체장비로부터 최소 얼마 이상 떨어져야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4[m]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 석면 취급작업과정을 보여주고 있다. 이 작업의 안전작업수칙에 대하여 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 석면취급 작업시 석면분진이 다른 근로자에게 확산되지 않도록 다른 작업장소와 격리하여 실시한다.
+② 석면은 밀폐설비 또는 국소배기 장치가 설치된 장소에서 취급한다.
+③ 석면을 직접 사용하는 작업 및 석면이 붙어 있는 물질을 파쇄 또는 해체하는 작업은 가능한 한 습식 상태로 작업을 실시한다.
+④ 석면작업장에서는 흡연 및 음식물을 섭취하지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동차도금작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교류아크용접작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전모.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VDT작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물해체작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>석면취급작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소결핍작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전블록.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소결핍작업 중 퍼지하는 상황이 있는데 아래 내용과 연관하여 퍼지의 목적을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 인화성 가스 및 지연성 가스의 경우
+② 급성독성 가스의 경우
+③ 불활성 가스의 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공장 배기구 같은데서 하얀 증기가 나오고 나서 한 작업자가 내부에서 그라인더로 연마하며 작업 장면을 보여준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 인화성 가스 및 지연성 가스 : 인화성 가스 및 지연성 가스에 대하여 화재 폭발 사고와 산소 결핍 사고의 방지
+② 급성독성 가스 : 급성독성 가스에 대하여 중독 사고의 방지
+③ 불활성 가스 : 불활성(비활성) 가스에 대하여 산소 결핍 사고의 방지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고무장갑, 고무장화를 착용하고 담배를 피우면서 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 항타기ㆍ항발기 작업하는 주위에서 2~3명의 작업자가 안전모를 착용하고 작업하는 중, 순간적으로 근처 전선에서 스파크가 발생한 사례이다. 고압선 주위에서 항타기ㆍ항발기 작업 시 관리적 대책 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해당 충전로를 이설할 것
+② 감전의 위험을 방지하기 위한 방책을 설치할 것
+③ 해당 충전로에 절연용 방호구를 설치할 것
+④ 감시하는 사람을 두고 작업을 감시하도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 승강기 컨트롤 패널을 맨손으로 점검(전압측정) 중 발생한 재해사례이다. 감전 방지대책 2가지를 서술하시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 MCC패널 점검 중으로 개폐기에는 통전중이라는 표지가 붙어 있고 작업자(면장갑 착용)가 개폐기문을 열어 전원을 차단하고 문을 닫은 후 다른 곳 패널에서 작업하려다 쓰러진 상황이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 각 차단기 별로 회로명을 표기하여 오동작을 막는다.
+② 잠금장치(시건장치) 및 표찰(TAG)을 사용하여 해당자 이외에 오작동을 막는다.
+③ 작업자에게 해당 작업시의 전기위험에 대한 안전교육을 실시한다.
+④ 작업자 간의 정확성을 기하기 위해 문저기 등의 연락가능장비를 이용하여 여러 차례 확인하는 절차를 준수한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면의 보호구 ① 명칭 ② 보호구가 갖추어야 할 구조를 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전블록
+② 갖추어야 하는 구조
+ - 추락 발생시 추락을 억제할 수 있는 자동잠김장치를 갖추어야 한다.
+ - 안전블록 부품은 부식방지처리를 해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식 크레인 작업시작전 점검사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 권과방지장치나 그 밖의 경보장치의 기능
+② 브레이크ㆍ클러치 및 조정장치의 기능
+③ 와이어로프가 통하고 있는 곳 및 작업장소의 지반상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 작업자가 퓨즈 교체 작업 중 감전사고가 발생했다. 산업안전보건법상 누전차단기 설치 장소 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 대지전압이 150[V]를 초과하는 이동형 또는 휴대형 전기 기계ㆍ기구
+② 물 등 도전성이 높은 액체가 있는 습윤장소에서 사용하는 저압(1,500[V] 이하 직류전압이나 1,000[V] 이하의 교류적압을 말한다)용 전기기계ㆍ기구
+③ 철판ㆍ철골 위 등 도전성이 높은 장소에서 사용하는 이동형 또는 휴대형 전기기계ㆍ기구
+④ 임시배선의 전로가 설치되는 장소에서 사용하는 이동형 또는 휴대형 전기기계ㆍ기구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업자가 전주에 올라가다 표지판에 부딪혀 추락하는(사람이 떨어지는)재해가 발생했다. 재해발생 원인 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락방호용 안전대 미착용 및 수직구명줄 미설치로 재해발생
+② 안전대 또는 고소작업대를 사용하지 않아 재해발생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 이동식 비계의 설치상태가 불량하여 발생된 재해 사례이다. 이동식 비계의 올바른 설치(조립)기준을 산업안전보건기준에 관한 규칙을 적용하여 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 이동식 비계의 바퀴에는 뜻밖의 갑작스러운 이동 또는 전도를 방지하기 위하여 브레이크ㆍ쐐기 등으로 바퀴를 고정시킨다음 비계의 일부를 견고한 시설물에 고정하거나 아웃트리거를 설치하는 등 필요한 조치를 할 것
+② 승강용사다리는 견고하게 설치할 것
+③ 비계의 최상부에서 작업을 하는 경우에는 안전난간을 설치할 것
+④ 작업발판은 항상 수평을 유지하고 작업발판 위에서 안전난간을 딛고 작업을 하거나 받침대 또는 사다리를 사용하여 작업하지 않도록 할 것
+⑤ 작업발판의 최대적재하중은 250[kg]을 초과하지 않도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 지게차 주행안전작업을 하고 있다. 지게차의 작업시작전 점검사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제동장치 및 조종장치 기능의 이상 유무
+② 하역장치 및 유압장치 기능의 이상 유무
+③ 바퀴의 이상 유무
+④ 전조등ㆍ후미등ㆍ방향지시기 및 경보장치 기능의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>높이가 2[m] 이상인 작업장소에서 근로자가 작업발판 위에서 작업을 하고 있다. 작업발판 설치기준 3가지를(단, 작업발판 폭과 틈은 제외)쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 발판재료는 작업시의 하중을 견딜 수 있도록 견고한 구조로 할 것
+② 작업발판의 폭은 40[cm] 이상으로 하고, 발판재료 간의 틈은 3[cm] 이하로 할 것. 다만, 외줄비계의 경우에는 고용노동부장관이 별도로 정하는 기준에 따른다.
+③ 추락의 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업의 성질상 안전난간을 설치하는 것이 곤란한 경우, 작업의 필요상 임시로 안전난간을 해체할 때에 추락방호망을 설치하거나 근로자로 하여금 안전대를 사용하도록 하는 등 추락위험 방지 조치를 한 경우에는 그러하지 아니하다.
+④ 작어발판의 지지물은 하중에 의하여 파괴될 우려가 없는 것을 사용할 것
+⑤ 작업발판 재료는 뒤집히거나 떨어지지 않도록 둘 이상의 지지물에 연결하거나 고정시킬 것
+⑥ 작업발판을 작업에 따라 이동시킬 경우에는 위험 방지에 필요한 조치를 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 승강기 설치작업을 하고 있다. 승강기 방호장치 6가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 과부하 방지장치
+② 권과방지 장치
+③ 비상정지장치
+④ 제동장치
+⑤ 파이널 리미트 스위치
+⑥ 속도 조절기
+⑦ 출입문인터록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 선박 밸러스트 탱크 내부의 슬러지를 제거하는 작업 도중에 작업자가 가스질식으로 의식을 잃었다. 이와 같은 사고에 대비하여 필요한 호흡용 보호구를 1가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>송기마스크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에서는 프레스 작업 중 작업자가 실수로 페달을 밟아 슬라이드가 하강하여 금형 사이에 손이낀 사례이다. 이러한 재해의 재발을 방지하기 위하여 ① 페달에는 무엇을 설치하고 ② 상형과 하형사이의 간격을 얼마 이하로 하는 것이 바람직한가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 설치장치 :
+② 설치간격 :</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① U자형 덮개
+② 8[mm] 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식 크레인의 작업시작전 점검사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 인쇄용 롤러를 청소하는 작업 중에 발생한 재해사례이다. 이 동영상을 보고 작업시 핵심 위험 요인과 안전대책을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업자가 인쇄용 윤전기의 전원을 끄지 않고 빙글빙글 서로 맞물려서 돌아가는 롤러를 걸레로 닦고 있다. 닦을 때 체중을 실어서 힘 있게 닦고, 위험하게 맞물리는 지점까지 걸레를 집어넣고 닦는다. 그 순간 작업자의 손이 롤러기 사이에 끼어서 사고를 당하고 사고 발생 후 전원을 차단하고 손을 빼내는 화면을 보여준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 핵심 위험요인
+ ① 회전체에 장갑을 착용하여 손이 다칠 우려가 있다.
+ ② 작업자가 전원을 차단하지 않고 작업을 하였다.
+ ③ 안전장치 없이 작업을 하여 다칠 우려가 있다.
+2) 안전대책
+ ① 회전체에는 장갑을 착용하지 않는다.
+ ② 이물질 제거시 롤러기의 전원을 차단하여 기계 작동을 방지한다.
+ ③ 안전장치가 없어서 롤러가 멈추지 않아 손이 물려 들어가므로 안전장치를 설치한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상과 같은 중량물 취급작업시 작업계획서의 내용 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회전체 물체를 분해하고 닦고 조립하고 있다. 2인 1조 작업인데 작업자 1명이 중량물이 무거워서 허리를 삐끗하고 중량물을 놓쳐서 다른 작업자 발등에 중량물이 떨어진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 추락위험을 예방할 수 있는 안전대책
+② 낙하위험을 예방할 수 있는 안전대책
+③ 전도위험을 예방할 수 있는 안전대책
+④ 협착위험을 예방할 수 있는 안전대책
+⑤ 붕괴위험을 예방할 수 있는 안전대책</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 이동식 비계의 설치상태가 불량하여 발생된 재해 사례이다. 이동식 비계의 올바른 설치(조립)기준을 산업안전보건기준에 관한 규칙을 적용하여 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 교량 하부 점검 중 발생한 재해사례이다. 영상을 참고하여 사고 원인 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 안전대 부착 설비 및 안전대 착용을 하지 않았다.
+② 안전난간 설치 불량
+③ 수직방호망 미설치(추락방호망 미설치)
+④ 작업자 주변 정리정돈 불량
+⑤ 작업 전 작업발판 등 부속설비 점검 미비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 따라서, 충전전로에서의 전기작업 중 조치 사항에 대해서 다음(①, ②)을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 충전전로를 취급하는 근로자에게 그 작업에 적합한( ① )를 착용시킬 것.
+2) 충전전로에 근접한 장소에서 전기작업을 하는 경우에는 해당 전압에 적합한( ② )를 설치할 것. 다만, 저압인 경우에는 해당 전기작업자가 ( ① )를 착용하되, 충전전로에 접촉할 우려가 없는 경우에는 ( ② )를 설치하지 아니할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 절연용 보호구
+② 절연용 방호구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면의 밀폐된 공간에서 그라인더 작업시 위험요인 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업시작 전 산소농도 및 유해가스 농도 등의 미 측정과 작업 중에도 계속 환기를 시키지 않아 위험
+② 환기를 실시할 수 없거나 산고결핍 위험 장소에 들어갈 때 호흡용 보호구를 착용하지 않아 위험
+③ 국소배기장치의 전원부에 잠금장치가 없고, 감시인을 배치하지 않아 위험</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건기준에 관한 규칙에 따라서, 용융고열물을 취급하는 설비를 내부에 설치한 건축물에 대하여 수증기 폭발을 방지하기 위하여 사업주가 해야하는 조치 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 바닥은 물이 고이지 아니하는 구조로 할 것
+② 지붕ㆍ벽ㆍ창 등은 빗물이 새어들지 아니하는 구조로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 탱크 내부 밀폐된 공간에서 작업자가 그라인더 작업을 하고 있고, 다른 작업자가 외부에 설치된 국소배기장치를 발로 차서 전원공급이 차단되어 내부 작업자가 의식을 잃고 쓰러지는 화면을 보여 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철광 용광로 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>절연보호구 미착용 작업자가 보이고, 크레인이 전선에 근접한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 재해사례에서 나타나는 위험점을 기계의 운동 형태에 따라 분류하고자 할 때 해당되는 위험점의 명칭과 그 정의를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근로자가 회전물(선반)에 샌드페이퍼를 감아 손으로 지지하고 있다. 작업복과 장갑이 말려들어 가는 동영상이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 위험점의 명칭 : 회전 말림점
+② 정의 : 회전축ㆍ커플링 등과 같이 회전하는 물체에 작업복 등이 말려드는 위험이 존재하는 점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면의 도영상은 습윤상태에서 작업 중 감전재해를 당한 사례이다. 동영상을 참고하여 동종의 재해가 발생하지 않도록 예방조치사항 3가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>단무지가 있고 무릎 정도 물이 차 있는 상태에서 펌프 작동과 동시에 감전되는 동영상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 모터와 전선의 이음새 부분을 작업 전 확인 또는 작업 전 펌프의 작동여부를 확인한다.
+② 수중 및 습윤한 장소에서 사용하는 전선은 수분의 침투가 불가능한 것을 사용한다.
+③ 감전 방지용 누전 차단기를 설치한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 사업내 안전보건교육에 있어, 밀폐공간에서의 작업 시의 특별교육 내용을 3가지 쓰시오.(단, 그 밖에 안전보건관리에 필요한 사항은 제외)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 산소농도 측정 및 작업환경에 관한 사항
+② 사고 시의 응급처치 및 비상시 구출에 관한 사항
+③ 보호구 착용 및 보호장비 사용에 관한 사항
+④ 장비ㆍ설비 및 시설 등의 안전점검에 관한 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면의 재해를 막기 위한 안전장구 2가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피트에서 물을 퍼내는 도중에 떨어져서 물에 빠진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 작업발판
+② 안전난간
+③ 울타리
+④ 수직형 추락방망</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 낙하물 방지망을 보수하는 장면을 보여주고 있다. 산업안전보건법령상 방호선반 설치 시 준수사항(  )를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 높이 ( ① )[m] 이내마다 설치하고, 내민 길이는 벽면으로부터 ( ② )[m] 이상으로 할 것
+2) 수평면과의 각도는 ( ③ )[º] 이상 ( ④ )[º] 이하를 유지할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 10
+② 2
+③ 20
+④ 30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>터널 작업 시 근로자 입장에서 위험요인을 2가지만 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>터널 내부 굴착 중, 컨베이어로 굴착토를 운반하는 중 분진이 날린다. 굴착 후 돌가루가 컨베이어에 떨어져 분진이 발생된다. 컨베이어로 모래, 돌가루를 밖으로 내보낸다. 컨베이어에 덮개 또는 울은 보이지 않는다. TBM 기계 안으로 작업자 2~3명이 드나든다. 주변에 방진마스크를 착용하지 않은 작업자가 5~6명 정도 서 있다. TBM 기계에서 분진이 스물스물 계속 올라온다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 분진 발생
+② 환기 및 조명 불량
+③ 작업통로 상태 불량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 전압이 흐르는 고압선 아래에서 작업 중 발생한 재해사례이다. 산업안전보건기준에 관한 규칙에 따라서, 충전전로에서의 전기작업 중 조치 사항에 대해서 다음 (  )을 채우시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 절연용 보호구
+② 전연용 방호구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 충전전로를 취급하는 근로자에게 그 작업에 적합한 ( ① )를 착용시킬 것
+2) 충전전로에 근접한 장소에서 전기작업을 하는 경우에는 해당 전압에 적합한 ( ② )를 설치할 것. 다만, 저압인 경우에는 해당 전기작업자가 ( ① )를 착용하되, 충전전로에 접촉할 우려가 없는 경우에는 ( ② )를 설치하지 아니할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 제동장치 및 조종장치 기능의 이상 유무
+② 하역장치 및 유압장치 기능의 이상 유무
+③ 바퀴의 이상 유무
+④ 전조등ㆍ후미등ㆍ방향지시등 및 경보장치 기능의 이상 유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 전주를 옮기다가 작업자가 전주에 맞아 사고를 당하였다. ① 재해요인(형태) ② 재해 정의를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 재해요인(형태) : 비래(물체에 맞음)
+② 정의 : 물건이 주체가 되어 사람이 맞는 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상 동영상의 작업을 하는 경우, 사업주는 근로자의 위험을 방지하기 위하여 작업 계획서를 작성하고 그 계획에 따라 작업을 하도록 하여야 한다. 그 작업계획서에 포함되어야 할 사항을 2가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 해당 작업에 따른 추락ㆍ낙하ㆍ전도ㆍ협착 및 붕괴 등의 위험 예방대책
+② 차량계 하역운반기계 등의 운행경로 및 작업방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면상의 작업에서 근로자가 착용해야할 보호구를 4가지 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 귀마개
+② 보안경
+③ 안전모
+④ 안전화
+⑤ 방진장갑
+⑥ 방진마스크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바닥의 콘크리트를 파쇄하는 작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 등유나 경유를 주입할 때 주의사항 관련하여 (  )에 알맞은 것을 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린이 남아있는 설비에 등유 주입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 전위차
+② 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 등유나 경유를 주입하기 전에 탱크ㆍ드럼 등과 주입설비 사이에 접속선이나 접지선을 연결하여 ( ① )를 줄이도록 할 것
+2) 등유나 경유를 주입하는 경우에는 그 액표면의 높이가 주입관의 선단의 높이를 넘을 때까지 주입속도를 초당 ( ② )미터 이하로 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>동영상은 프레스기로 철판에 구멍을 뚫는 작업 중이다. 작업시작 전 점검사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 클러치 및 브레이크의 기능
+② 크랭크축ㆍ플라이휠ㆍ슬라이드ㆍ연결봉 및 연결 나사의 풀림 여부
+③ 1행정 1정지기구ㆍ급정지장치 및 비상정지장치의 기능
+④ 슬라이드 또는 칼날에 의한 위험방지 기구의 기능
+⑤ 프레스의 금형 및 고정볼트 상태
+⑥ 방호장치의 기능
+⑦ 전단기의 칼날 및 테이블의 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산업안전보건법령상, 사업주가 흙막이 지보공을 설치하였을 때는 ① 설치 목적과 ② 정기적으로 점검하고 이상을 발견하면 즉시 보수하여야 하는 사항 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 설치목적 : 토사 붕괴 방지(무너짐 방지)
+② 이상 발견 시 즉시 보수하여야 할 사항
+ㆍ부재의 손상ㆍ변형ㆍ부식ㆍ변위 및 탈락의 유무와 상태
+ㆍ버팀대의 긴압의 정도
+ㆍ부재의 접속부ㆍ부착부 및 교차부의 상태
+ㆍ침하의 정도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에서 나타난 작업장에 국소배기장치를 설치할 때 덕트의 기준 3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 가능하면 길이는 짧게 하고 굴곡부의 수는 적게 할 것
+② 접속부의 안쪽은 돌출된 부분이 없도록 할 것
+③ 청소구를 설치하는 등 청소하기 쉬운 구조로 할 것
+④ 덕트 내부에 오염물질이 쌓이지 않도록 이송속도를 유지할 것
+⑤ 연결 부위 등은 외부 공기가 들어오지 않도록 할 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산소농도 및 유해가스 농도를 측정할 수 있는 사람 및 기관 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 관리감독자
+② 안전관리자, 보건관리자
+③ 안전관리전문기관, 보건관리전문기관
+④ 건설재해예방전문지도기관
+⑤ 작업환경측정기관
+⑥ 한국산업안전보건공단이 정하는 산소 및 유해가스 농도의 측정ㆍ평가에 관한 교육을 이수한 사람</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 30[kV] 전압이 흐르는 고압선 아래에서 작업 중 발생한 재해사례이다. 이동식 크레인을 이용하여 고압선 주위에서 작업할 경우 사업주의 감전 조치사항(동종 재해예방을 위한 작업지휘자)3가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 차량 등을 충전부로부터 300[cm] 이상 이격시키되, 대지전압이 50[kV]를 넘는 경우 10[kV] 증가할 때마다 10[cm] 씩 증가한다.
+② 접지된 차량등이 충전전로와 접촉할 우려가 있을 경우 지상의 근로자가 접지점에 접촉하지 않도록 조치한다.
+③ 차량과 근로자가 접촉하지 않도록 울타리를 설치하거나 감시인을 배치한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면은 박공지붕 설치 작업 중 발생한 재해사례이다. 해당 화면은 박공지붕에서 비래에 의해 재해가 발생하였음을 나타내고 있다. 안전대책 4가지를 쓰시오.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 근로자는 위험한 장소에서 휴식을 취하지 않는다.
+② 추락방호망을 설치한다.
+③ 한 곳에 과적하여 적치하지 않는다.
+④ 안전대 부착설비를 설치하고, 안전대를 착용한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박공지붕 위쪽과 바닥을 보여준다. 오른쪽에 안전난간, 추락방지망이 미설치된 모습이 보이고, 지붕 위쪽 중간에서 커피를 마시면서 앉아 휴식을 취하는 작업자(안전모, 안전화 착용함)들이 보인다. 작업자 왼쪽과 뒤편에 적재물이 적치되어 있는데, 뒤에 있던 삼각형 적재물이 굴러와 작업자 등에 맞아 작업자가 앞으로 쓰러지는 동영상이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>덤프유압장치밸브수리작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DMF작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전주고소작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고소작업대작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항타기, 항발기 작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방독마스크작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>판넬작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철근조립작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>차단기(퓨즈)교체작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비계설치.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업발판 위 작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>승강기설치작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밸러스트 탱크 내부작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롤러기작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중량물취급작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교량하부작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>활선작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">용광로작업.png </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀폐공간작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회전물(선반)작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>습윤상태작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물빼기작업.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낙하물방지망보수작업.jpg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>터널굴착작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식크레인작업2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지게차주행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동식크레인작업1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콘크리트파쇄작업</t>
+  </si>
+  <si>
+    <t>지게차경유주입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프레스작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흙막이지보공작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국소배기장치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀폐공간작업</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지붕설치작업</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -709,6 +1401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
@@ -886,6 +1579,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E1CD94-D288-4A57-AC69-EDD02BC9BCAA}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
@@ -925,6 +1619,9 @@
       <c r="B2" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>30</v>
       </c>
@@ -936,6 +1633,9 @@
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>174</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>41</v>
       </c>
@@ -947,6 +1647,9 @@
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>175</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>43</v>
       </c>
@@ -958,6 +1661,9 @@
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
@@ -969,6 +1675,9 @@
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="C6" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
@@ -980,6 +1689,9 @@
       <c r="A7" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="C7" s="1" t="s">
+        <v>178</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>51</v>
       </c>
@@ -994,6 +1706,9 @@
       <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="C8" s="1" t="s">
+        <v>179</v>
+      </c>
       <c r="D8" s="1" t="s">
         <v>53</v>
       </c>
@@ -1005,6 +1720,9 @@
       <c r="A9" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="C9" s="1" t="s">
+        <v>180</v>
+      </c>
       <c r="D9" s="1" t="s">
         <v>55</v>
       </c>
@@ -1015,6 +1733,12 @@
     <row r="10" spans="1:6" ht="69.599999999999994">
       <c r="A10" s="1" t="s">
         <v>56</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>57</v>
@@ -1031,7 +1755,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D2433A3-894D-42EC-B9D8-5384B49B20B8}">
-  <dimension ref="A1:F7"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
@@ -1067,6 +1792,9 @@
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>59</v>
       </c>
@@ -1078,6 +1806,9 @@
       <c r="A3" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>61</v>
       </c>
@@ -1092,6 +1823,9 @@
       <c r="A4" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>64</v>
       </c>
@@ -1099,7 +1833,830 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="98.4" customHeight="1"/>
+    <row r="5" spans="1:6" ht="87">
+      <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="139.19999999999999">
+      <c r="A6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4">
+      <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="121.8">
+      <c r="A9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="87">
+      <c r="A10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279CC508-3724-4FD6-8B32-96A930C78F8F}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2">
+      <c r="A2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="156.6">
+      <c r="A3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="52.2">
+      <c r="A4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="208.8">
+      <c r="A5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87">
+      <c r="A6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="121.8">
+      <c r="A8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87">
+      <c r="A9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="104.4">
+      <c r="A10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97A13BC5-E573-4A98-8E9E-EC1CCBF4B811}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="52.2">
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="174">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87">
+      <c r="A4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="208.8">
+      <c r="A5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="87">
+      <c r="A6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="104.4">
+      <c r="A8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87">
+      <c r="A9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2">
+      <c r="A10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6CE6AD-7F7F-413C-A761-77E5AF8DAB9B}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="87">
+      <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="174">
+      <c r="A3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="87">
+      <c r="A4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="69.599999999999994">
+      <c r="A5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="69.599999999999994">
+      <c r="A6" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="121.8">
+      <c r="A8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="87">
+      <c r="A9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.2">
+      <c r="A10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2353A3AD-FF6C-43D3-B073-8E26E49AB184}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="35.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.09765625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.8984375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="104.4">
+      <c r="A2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="104.4">
+      <c r="A3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="104.4">
+      <c r="A4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="139.19999999999999">
+      <c r="A5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="104.4">
+      <c r="A6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="98.4" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="121.8">
+      <c r="A8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="121.8">
+      <c r="A9" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="139.19999999999999">
+      <c r="A10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/산업안전기사_작업형_문제은행.xlsx
+++ b/산업안전기사_작업형_문제은행.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wpgk1\Desktop\Web_CBT_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B4CE5F-286C-4B6D-9C61-3B9CE0716B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDD89A0-37E1-48C0-AF64-83B6C29F08CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="17년 과년도" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="207">
   <si>
     <t>점수</t>
   </si>
@@ -736,11 +736,6 @@
   </si>
   <si>
     <t>화면은 전압이 흐르는 고압선 아래에서 작업 중 발생한 재해사례이다. 산업안전보건기준에 관한 규칙에 따라서, 충전전로에서의 전기작업 중 조치 사항에 대해서 다음 (  )을 채우시오.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>① 절연용 보호구
-② 전연용 방호구</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1620,7 +1615,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>30</v>
@@ -1634,7 +1629,7 @@
         <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>41</v>
@@ -1648,7 +1643,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>43</v>
@@ -1662,7 +1657,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>45</v>
@@ -1676,7 +1671,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>47</v>
@@ -1690,7 +1685,7 @@
         <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>51</v>
@@ -1707,7 +1702,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>53</v>
@@ -1721,7 +1716,7 @@
         <v>54</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>55</v>
@@ -1900,7 +1895,7 @@
         <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>86</v>
@@ -1983,7 +1978,7 @@
         <v>91</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>92</v>
@@ -1997,7 +1992,7 @@
         <v>93</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>94</v>
@@ -2011,7 +2006,7 @@
         <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>96</v>
@@ -2039,7 +2034,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>100</v>
@@ -2053,7 +2048,7 @@
         <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>102</v>
@@ -2067,7 +2062,7 @@
         <v>103</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>104</v>
@@ -2081,7 +2076,7 @@
         <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>107</v>
@@ -2156,7 +2151,7 @@
         <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>111</v>
@@ -2173,7 +2168,7 @@
         <v>113</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>114</v>
@@ -2187,7 +2182,7 @@
         <v>115</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>96</v>
@@ -2201,7 +2196,7 @@
         <v>116</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>117</v>
@@ -2218,7 +2213,7 @@
         <v>127</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>120</v>
@@ -2238,7 +2233,7 @@
         <v>125</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>122</v>
@@ -2255,7 +2250,7 @@
         <v>126</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>124</v>
@@ -2272,7 +2267,7 @@
         <v>129</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>130</v>
@@ -2330,7 +2325,7 @@
         <v>132</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>133</v>
@@ -2347,7 +2342,7 @@
         <v>110</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>111</v>
@@ -2364,7 +2359,7 @@
         <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>135</v>
@@ -2381,7 +2376,7 @@
         <v>137</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>138</v>
@@ -2395,7 +2390,7 @@
         <v>139</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>141</v>
@@ -2415,7 +2410,7 @@
         <v>143</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>144</v>
@@ -2432,16 +2427,16 @@
         <v>20</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="E8" s="1">
-        <v>4</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="87">
@@ -2449,10 +2444,10 @@
         <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
@@ -2460,13 +2455,13 @@
     </row>
     <row r="10" spans="1:6" ht="52.2">
       <c r="A10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
@@ -2515,13 +2510,13 @@
     </row>
     <row r="2" spans="1:6" ht="104.4">
       <c r="A2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="E2" s="1">
         <v>5</v>
@@ -2529,16 +2524,16 @@
     </row>
     <row r="3" spans="1:6" ht="104.4">
       <c r="A3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="E3" s="1">
         <v>4</v>
@@ -2546,33 +2541,33 @@
     </row>
     <row r="4" spans="1:6" ht="104.4">
       <c r="A4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="E4" s="1">
-        <v>4</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="139.19999999999999">
       <c r="A5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="E5" s="1">
         <v>6</v>
@@ -2580,13 +2575,13 @@
     </row>
     <row r="6" spans="1:6" ht="104.4">
       <c r="A6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
@@ -2594,13 +2589,13 @@
     </row>
     <row r="7" spans="1:6" ht="98.4" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
@@ -2608,16 +2603,16 @@
     </row>
     <row r="8" spans="1:6" ht="121.8">
       <c r="A8" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>125</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
@@ -2625,16 +2620,16 @@
     </row>
     <row r="9" spans="1:6" ht="121.8">
       <c r="A9" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
@@ -2642,16 +2637,16 @@
     </row>
     <row r="10" spans="1:6" ht="139.19999999999999">
       <c r="A10" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
